--- a/cloud_storage/брак.xlsx
+++ b/cloud_storage/брак.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,24 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Пример брака</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>открыт</t>
         </is>
       </c>
     </row>
